--- a/static/data/exports/Retro_PY_AE_2021.xlsx
+++ b/static/data/exports/Retro_PY_AE_2021.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>51</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -638,6 +651,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>58</v>
+      </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
@@ -700,6 +726,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>36</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -763,7 +802,7 @@
         </is>
       </c>
       <c r="Q5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>42</v>
@@ -824,6 +863,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>39</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -886,6 +938,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>51</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
@@ -948,6 +1013,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>33</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1088,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>33</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1072,6 +1163,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>33</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1238,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>45</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1313,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>46</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1388,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>63</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1463,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>48</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1538,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>51</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1613,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>52</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1506,6 +1688,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>39</v>
+      </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
@@ -1568,6 +1763,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>32</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,6 +1838,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>25</v>
+      </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
@@ -1692,6 +1913,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>51</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1755,7 +1989,7 @@
         </is>
       </c>
       <c r="Q21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>42</v>
@@ -1816,6 +2050,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>30</v>
+      </c>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
@@ -1878,6 +2125,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>47</v>
+      </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -1940,6 +2200,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>39</v>
+      </c>
       <c r="Q24" t="b">
         <v>0</v>
       </c>
@@ -2002,6 +2275,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>44</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2350,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>50</v>
+      </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
@@ -2126,6 +2425,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>38</v>
+      </c>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
@@ -2188,6 +2500,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>32</v>
+      </c>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
@@ -2250,6 +2575,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>49</v>
+      </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
@@ -2312,6 +2650,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>48</v>
+      </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
@@ -2374,6 +2725,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>45</v>
+      </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2800,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>42</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2498,6 +2875,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>42</v>
+      </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
@@ -2561,7 +2951,7 @@
         </is>
       </c>
       <c r="Q34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>42</v>
@@ -2622,6 +3012,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>62</v>
+      </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3087,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>49</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,6 +3162,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>38</v>
+      </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -2808,6 +3237,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>48</v>
+      </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
@@ -2870,6 +3312,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>37</v>
+      </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
@@ -2932,6 +3387,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>61</v>
+      </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -2994,6 +3462,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>45</v>
+      </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
@@ -3056,6 +3537,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>68</v>
+      </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3612,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>50</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3180,6 +3687,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>25</v>
+      </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
@@ -3243,7 +3763,7 @@
         </is>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>42</v>
@@ -3304,6 +3824,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>38</v>
+      </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3899,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>53</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,6 +3974,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>45</v>
+      </c>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
@@ -3490,6 +4049,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>35</v>
+      </c>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
@@ -3552,6 +4124,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>34</v>
+      </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +4199,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>67</v>
+      </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
@@ -3676,6 +4274,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>35</v>
+      </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
@@ -3738,6 +4349,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>58</v>
+      </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
@@ -3800,6 +4424,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>54</v>
+      </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
@@ -3862,6 +4499,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>55</v>
+      </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -3924,6 +4574,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>37</v>
+      </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
@@ -3986,6 +4649,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>46</v>
+      </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4049,7 +4725,7 @@
         </is>
       </c>
       <c r="Q58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>42</v>
@@ -4110,6 +4786,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>47</v>
+      </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
@@ -4172,6 +4861,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>51</v>
+      </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
@@ -4234,6 +4936,19 @@
           <t>PUDEP</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>29</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4296,6 +5011,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>45</v>
+      </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
@@ -4358,6 +5086,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>56</v>
+      </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +5161,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>28</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4482,6 +5236,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>46</v>
+      </c>
       <c r="Q65" t="b">
         <v>0</v>
       </c>
@@ -4544,6 +5311,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>60</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,6 +5386,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>40</v>
+      </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
@@ -4668,6 +5461,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>51</v>
+      </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
@@ -4730,6 +5536,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>39</v>
+      </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -4792,6 +5611,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>60</v>
+      </c>
       <c r="Q70" t="b">
         <v>0</v>
       </c>
@@ -4854,6 +5686,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>58</v>
+      </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
@@ -4916,6 +5761,19 @@
           <t>VCK</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>60</v>
+      </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -4978,6 +5836,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>42</v>
+      </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
@@ -5040,6 +5911,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>46</v>
+      </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5103,7 +5987,7 @@
         </is>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>42</v>
@@ -5164,6 +6048,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>54</v>
+      </c>
       <c r="Q76" t="b">
         <v>0</v>
       </c>
@@ -5226,6 +6123,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>61</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5288,6 +6198,19 @@
           <t>CPI(ML)(L)</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>42</v>
+      </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
@@ -5350,6 +6273,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>41</v>
+      </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
@@ -5412,6 +6348,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>43</v>
+      </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
@@ -5474,6 +6423,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>42</v>
+      </c>
       <c r="Q81" t="b">
         <v>0</v>
       </c>
@@ -5536,6 +6498,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>33</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5598,6 +6573,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>41</v>
+      </c>
       <c r="Q83" t="b">
         <v>0</v>
       </c>
@@ -5660,6 +6648,19 @@
           <t>PUDEP</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>40</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5722,6 +6723,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>44</v>
+      </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
@@ -5784,6 +6798,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>64</v>
+      </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -5846,6 +6873,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>41</v>
+      </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
@@ -5908,6 +6948,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>49</v>
+      </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
@@ -5970,6 +7023,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>40</v>
+      </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6033,7 +7099,7 @@
         </is>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>42</v>
@@ -6094,6 +7160,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>46</v>
+      </c>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
@@ -6156,6 +7235,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>54</v>
+      </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
@@ -6218,6 +7310,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>47</v>
+      </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
@@ -6280,6 +7385,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>57</v>
+      </c>
       <c r="Q94" t="b">
         <v>0</v>
       </c>
@@ -6342,6 +7460,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>53</v>
+      </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
@@ -6404,6 +7535,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>47</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
@@ -6466,6 +7610,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>46</v>
+      </c>
       <c r="Q97" t="b">
         <v>0</v>
       </c>
@@ -6529,7 +7686,7 @@
         </is>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>42</v>
@@ -6590,6 +7747,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>41</v>
+      </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -6652,6 +7822,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>47</v>
+      </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
@@ -6714,6 +7897,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>35</v>
+      </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +7972,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>43</v>
+      </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
@@ -6838,6 +8047,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>70</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6900,6 +8122,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>49</v>
+      </c>
       <c r="Q104" t="b">
         <v>0</v>
       </c>
@@ -6962,6 +8197,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>45</v>
+      </c>
       <c r="Q105" t="b">
         <v>0</v>
       </c>
@@ -7024,6 +8272,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>56</v>
+      </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
@@ -7087,7 +8348,7 @@
         </is>
       </c>
       <c r="Q107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>42</v>
@@ -7148,6 +8409,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>35</v>
+      </c>
       <c r="Q108" t="b">
         <v>0</v>
       </c>
@@ -7210,6 +8484,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>57</v>
+      </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
@@ -7272,6 +8559,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>57</v>
+      </c>
       <c r="Q110" t="b">
         <v>0</v>
       </c>
@@ -7334,6 +8634,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>55</v>
+      </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
@@ -7396,6 +8709,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>40</v>
+      </c>
       <c r="Q112" t="b">
         <v>0</v>
       </c>
@@ -7458,6 +8784,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>45</v>
+      </c>
       <c r="Q113" t="b">
         <v>0</v>
       </c>
@@ -7520,6 +8859,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>56</v>
+      </c>
       <c r="Q114" t="b">
         <v>0</v>
       </c>
@@ -7582,6 +8934,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>57</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7644,6 +9009,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>32</v>
+      </c>
       <c r="Q116" t="b">
         <v>0</v>
       </c>
@@ -7707,7 +9085,7 @@
         </is>
       </c>
       <c r="Q117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>42</v>
@@ -7768,6 +9146,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>55</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7830,6 +9221,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>33</v>
+      </c>
       <c r="Q119" t="b">
         <v>0</v>
       </c>
@@ -7892,6 +9296,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>43</v>
+      </c>
       <c r="Q120" t="b">
         <v>0</v>
       </c>
@@ -7954,6 +9371,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>45</v>
+      </c>
       <c r="Q121" t="b">
         <v>0</v>
       </c>
@@ -8016,6 +9446,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>64</v>
+      </c>
       <c r="Q122" t="b">
         <v>0</v>
       </c>
@@ -8078,6 +9521,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>38</v>
+      </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
@@ -8140,6 +9596,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>47</v>
+      </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
@@ -8202,8 +9671,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>51</v>
+      </c>
       <c r="Q125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>42</v>
@@ -8264,6 +9746,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>40</v>
+      </c>
       <c r="Q126" t="b">
         <v>0</v>
       </c>
@@ -8326,6 +9821,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>42</v>
+      </c>
       <c r="Q127" t="b">
         <v>0</v>
       </c>
@@ -8389,7 +9897,7 @@
         </is>
       </c>
       <c r="Q128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
         <v>42</v>
@@ -8450,6 +9958,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>40</v>
+      </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
@@ -8512,6 +10033,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>50</v>
+      </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
@@ -8574,6 +10108,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>34</v>
+      </c>
       <c r="Q131" t="b">
         <v>0</v>
       </c>
@@ -8636,6 +10183,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>49</v>
+      </c>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
@@ -8698,6 +10258,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>39</v>
+      </c>
       <c r="Q133" t="b">
         <v>0</v>
       </c>
@@ -8715,11 +10288,11 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1728270</v>
+        <v>1728271</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Karunakaran</t>
+          <t>Anna Durai. M</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8752,13 +10325,26 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Karunakaran</t>
+          <t>Anna Durai. M</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>53</v>
       </c>
       <c r="Q134" t="b">
         <v>0</v>
@@ -8777,11 +10363,11 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1728271</v>
+        <v>1728270</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Anna Durai. M</t>
+          <t>Karunakaran</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8814,13 +10400,26 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Anna Durai. M</t>
+          <t>Karunakaran</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>35</v>
       </c>
       <c r="Q135" t="b">
         <v>0</v>
@@ -8884,6 +10483,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>43</v>
+      </c>
       <c r="Q136" t="b">
         <v>0</v>
       </c>
@@ -8946,6 +10558,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>47</v>
+      </c>
       <c r="Q137" t="b">
         <v>0</v>
       </c>
@@ -9008,6 +10633,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>47</v>
+      </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
@@ -9070,6 +10708,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>36</v>
+      </c>
       <c r="Q139" t="b">
         <v>0</v>
       </c>
@@ -9132,6 +10783,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>50</v>
+      </c>
       <c r="Q140" t="b">
         <v>0</v>
       </c>
@@ -9195,7 +10859,7 @@
         </is>
       </c>
       <c r="Q141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>42</v>
@@ -9256,6 +10920,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>45</v>
+      </c>
       <c r="Q142" t="b">
         <v>0</v>
       </c>
@@ -9318,6 +10995,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>51</v>
+      </c>
       <c r="Q143" t="b">
         <v>0</v>
       </c>
@@ -9380,6 +11070,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>27</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +11145,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>48</v>
+      </c>
       <c r="Q145" t="b">
         <v>0</v>
       </c>
@@ -9504,6 +11220,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>64</v>
+      </c>
       <c r="Q146" t="b">
         <v>0</v>
       </c>
@@ -9566,6 +11295,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>69</v>
+      </c>
       <c r="Q147" t="b">
         <v>0</v>
       </c>
@@ -9628,6 +11370,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>47</v>
+      </c>
       <c r="Q148" t="b">
         <v>0</v>
       </c>
@@ -9690,6 +11445,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>39</v>
+      </c>
       <c r="Q149" t="b">
         <v>0</v>
       </c>
@@ -9752,6 +11520,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>39</v>
+      </c>
       <c r="Q150" t="b">
         <v>1</v>
       </c>
@@ -9814,6 +11595,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>29</v>
+      </c>
       <c r="Q151" t="b">
         <v>0</v>
       </c>
@@ -9876,6 +11670,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>35</v>
+      </c>
       <c r="Q152" t="b">
         <v>0</v>
       </c>
@@ -9938,6 +11745,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>40</v>
+      </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
@@ -10000,6 +11820,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>39</v>
+      </c>
       <c r="Q154" t="b">
         <v>0</v>
       </c>
@@ -10063,7 +11896,7 @@
         </is>
       </c>
       <c r="Q155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
         <v>42</v>
@@ -10124,6 +11957,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>43</v>
+      </c>
       <c r="Q156" t="b">
         <v>0</v>
       </c>
@@ -10186,6 +12032,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>38</v>
+      </c>
       <c r="Q157" t="b">
         <v>0</v>
       </c>
@@ -10248,6 +12107,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>46</v>
+      </c>
       <c r="Q158" t="b">
         <v>0</v>
       </c>
@@ -10310,6 +12182,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>48</v>
+      </c>
       <c r="Q159" t="b">
         <v>0</v>
       </c>
@@ -10372,6 +12257,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>57</v>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
@@ -10434,6 +12332,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>60</v>
+      </c>
       <c r="Q161" t="b">
         <v>0</v>
       </c>
@@ -10496,6 +12407,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>62</v>
+      </c>
       <c r="Q162" t="b">
         <v>0</v>
       </c>
@@ -10558,6 +12482,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>37</v>
+      </c>
       <c r="Q163" t="b">
         <v>0</v>
       </c>
@@ -10620,6 +12557,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>35</v>
+      </c>
       <c r="Q164" t="b">
         <v>0</v>
       </c>
@@ -10683,7 +12633,7 @@
         </is>
       </c>
       <c r="Q165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>42</v>
@@ -10744,6 +12694,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>68</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10806,6 +12769,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>70</v>
+      </c>
       <c r="Q167" t="b">
         <v>0</v>
       </c>
@@ -10868,6 +12844,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>53</v>
+      </c>
       <c r="Q168" t="b">
         <v>0</v>
       </c>
@@ -10930,6 +12919,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>64</v>
+      </c>
       <c r="Q169" t="b">
         <v>0</v>
       </c>
@@ -10992,8 +12994,21 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>56</v>
+      </c>
       <c r="Q170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>42</v>
@@ -11054,6 +13069,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>63</v>
+      </c>
       <c r="Q171" t="b">
         <v>1</v>
       </c>
@@ -11116,6 +13144,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>35</v>
+      </c>
       <c r="Q172" t="b">
         <v>0</v>
       </c>
@@ -11178,6 +13219,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>36</v>
+      </c>
       <c r="Q173" t="b">
         <v>0</v>
       </c>
@@ -11241,7 +13295,7 @@
         </is>
       </c>
       <c r="Q174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>42</v>
@@ -11302,6 +13356,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>36</v>
+      </c>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
@@ -11364,6 +13431,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>59</v>
+      </c>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
@@ -11426,6 +13506,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>60</v>
+      </c>
       <c r="Q177" t="b">
         <v>0</v>
       </c>
@@ -11488,6 +13581,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>58</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13656,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>41</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11612,6 +13731,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>49</v>
+      </c>
       <c r="Q180" t="b">
         <v>0</v>
       </c>
@@ -11674,6 +13806,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>37</v>
+      </c>
       <c r="Q181" t="b">
         <v>0</v>
       </c>
@@ -11736,6 +13881,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>56</v>
+      </c>
       <c r="Q182" t="b">
         <v>0</v>
       </c>
@@ -11798,6 +13956,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>46</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11860,6 +14031,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>61</v>
+      </c>
       <c r="Q184" t="b">
         <v>0</v>
       </c>
@@ -11922,6 +14106,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>36</v>
+      </c>
       <c r="Q185" t="b">
         <v>0</v>
       </c>
@@ -11984,6 +14181,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>46</v>
+      </c>
       <c r="Q186" t="b">
         <v>0</v>
       </c>
@@ -12047,7 +14257,7 @@
         </is>
       </c>
       <c r="Q187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
         <v>42</v>
@@ -12108,6 +14318,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>45</v>
+      </c>
       <c r="Q188" t="b">
         <v>0</v>
       </c>
@@ -12170,6 +14393,19 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>42</v>
+      </c>
       <c r="Q189" t="b">
         <v>0</v>
       </c>
@@ -12232,6 +14468,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>39</v>
+      </c>
       <c r="Q190" t="b">
         <v>0</v>
       </c>
@@ -12294,6 +14543,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>48</v>
+      </c>
       <c r="Q191" t="b">
         <v>0</v>
       </c>
@@ -12356,6 +14618,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>39</v>
+      </c>
       <c r="Q192" t="b">
         <v>0</v>
       </c>
@@ -12418,6 +14693,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>50</v>
+      </c>
       <c r="Q193" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +14768,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>41</v>
+      </c>
       <c r="Q194" t="b">
         <v>0</v>
       </c>
@@ -12542,6 +14843,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>41</v>
+      </c>
       <c r="Q195" t="b">
         <v>0</v>
       </c>
@@ -12604,6 +14918,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>56</v>
+      </c>
       <c r="Q196" t="b">
         <v>0</v>
       </c>
@@ -12666,6 +14993,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>31</v>
+      </c>
       <c r="Q197" t="b">
         <v>0</v>
       </c>
@@ -12728,6 +15068,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>29</v>
+      </c>
       <c r="Q198" t="b">
         <v>0</v>
       </c>
@@ -12790,6 +15143,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>54</v>
+      </c>
       <c r="Q199" t="b">
         <v>0</v>
       </c>
@@ -12852,6 +15218,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>69</v>
+      </c>
       <c r="Q200" t="b">
         <v>0</v>
       </c>
@@ -12914,6 +15293,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>39</v>
+      </c>
       <c r="Q201" t="b">
         <v>0</v>
       </c>
@@ -12977,7 +15369,7 @@
         </is>
       </c>
       <c r="Q202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R202" t="n">
         <v>42</v>
@@ -13038,6 +15430,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>34</v>
+      </c>
       <c r="Q203" t="b">
         <v>0</v>
       </c>
@@ -13100,6 +15505,19 @@
           <t>MIDP</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>40</v>
+      </c>
       <c r="Q204" t="b">
         <v>0</v>
       </c>
@@ -13162,6 +15580,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>31</v>
+      </c>
       <c r="Q205" t="b">
         <v>0</v>
       </c>
@@ -13224,6 +15655,19 @@
           <t>SDPI</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>53</v>
+      </c>
       <c r="Q206" t="b">
         <v>0</v>
       </c>
@@ -13286,6 +15730,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>41</v>
+      </c>
       <c r="Q207" t="b">
         <v>0</v>
       </c>
@@ -13348,6 +15805,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>49</v>
+      </c>
       <c r="Q208" t="b">
         <v>0</v>
       </c>
@@ -13410,6 +15880,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>32</v>
+      </c>
       <c r="Q209" t="b">
         <v>0</v>
       </c>
@@ -13472,6 +15955,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>63</v>
+      </c>
       <c r="Q210" t="b">
         <v>0</v>
       </c>
@@ -13534,6 +16030,19 @@
           <t>PUDEP</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>42</v>
+      </c>
       <c r="Q211" t="b">
         <v>0</v>
       </c>
@@ -13596,6 +16105,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>45</v>
+      </c>
       <c r="Q212" t="b">
         <v>0</v>
       </c>
@@ -13658,6 +16180,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>51</v>
+      </c>
       <c r="Q213" t="b">
         <v>0</v>
       </c>
@@ -13720,6 +16255,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>32</v>
+      </c>
       <c r="Q214" t="b">
         <v>0</v>
       </c>
@@ -13782,6 +16330,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>41</v>
+      </c>
       <c r="Q215" t="b">
         <v>0</v>
       </c>
@@ -13844,6 +16405,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>49</v>
+      </c>
       <c r="Q216" t="b">
         <v>1</v>
       </c>
@@ -13906,6 +16480,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>54</v>
+      </c>
       <c r="Q217" t="b">
         <v>0</v>
       </c>
@@ -13968,6 +16555,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>28</v>
+      </c>
       <c r="Q218" t="b">
         <v>0</v>
       </c>
@@ -14031,7 +16631,7 @@
         </is>
       </c>
       <c r="Q219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
         <v>42</v>
@@ -14092,6 +16692,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>27</v>
+      </c>
       <c r="Q220" t="b">
         <v>0</v>
       </c>
@@ -14154,6 +16767,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>50</v>
+      </c>
       <c r="Q221" t="b">
         <v>0</v>
       </c>
@@ -14216,6 +16842,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>36</v>
+      </c>
       <c r="Q222" t="b">
         <v>0</v>
       </c>
@@ -14278,8 +16917,21 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>41</v>
+      </c>
       <c r="Q223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R223" t="n">
         <v>42</v>
@@ -14340,6 +16992,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>29</v>
+      </c>
       <c r="Q224" t="b">
         <v>0</v>
       </c>
@@ -14402,6 +17067,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>37</v>
+      </c>
       <c r="Q225" t="b">
         <v>0</v>
       </c>
@@ -14464,6 +17142,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>41</v>
+      </c>
       <c r="Q226" t="b">
         <v>0</v>
       </c>
@@ -14526,6 +17217,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>40</v>
+      </c>
       <c r="Q227" t="b">
         <v>0</v>
       </c>
@@ -14588,6 +17292,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>57</v>
+      </c>
       <c r="Q228" t="b">
         <v>0</v>
       </c>
@@ -14650,6 +17367,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>61</v>
+      </c>
       <c r="Q229" t="b">
         <v>1</v>
       </c>
@@ -14712,6 +17442,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>27</v>
+      </c>
       <c r="Q230" t="b">
         <v>0</v>
       </c>
@@ -14774,6 +17517,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>61</v>
+      </c>
       <c r="Q231" t="b">
         <v>0</v>
       </c>
@@ -14836,6 +17592,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>51</v>
+      </c>
       <c r="Q232" t="b">
         <v>0</v>
       </c>
@@ -14899,7 +17668,7 @@
         </is>
       </c>
       <c r="Q233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
         <v>42</v>
@@ -14960,6 +17729,19 @@
           <t>SDPI</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>47</v>
+      </c>
       <c r="Q234" t="b">
         <v>0</v>
       </c>
@@ -15022,6 +17804,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>46</v>
+      </c>
       <c r="Q235" t="b">
         <v>0</v>
       </c>
@@ -15084,6 +17879,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>29</v>
+      </c>
       <c r="Q236" t="b">
         <v>0</v>
       </c>
@@ -15146,6 +17954,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>33</v>
+      </c>
       <c r="Q237" t="b">
         <v>0</v>
       </c>
@@ -15208,6 +18029,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>56</v>
+      </c>
       <c r="Q238" t="b">
         <v>0</v>
       </c>
@@ -15270,8 +18104,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>48</v>
+      </c>
       <c r="Q239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R239" t="n">
         <v>42</v>
@@ -15332,6 +18179,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>39</v>
+      </c>
       <c r="Q240" t="b">
         <v>0</v>
       </c>
@@ -15394,6 +18254,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>51</v>
+      </c>
       <c r="Q241" t="b">
         <v>0</v>
       </c>
@@ -15456,6 +18329,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>54</v>
+      </c>
       <c r="Q242" t="b">
         <v>0</v>
       </c>
@@ -15519,7 +18405,7 @@
         </is>
       </c>
       <c r="Q243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
         <v>42</v>
@@ -15580,6 +18466,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>33</v>
+      </c>
       <c r="Q244" t="b">
         <v>0</v>
       </c>
@@ -15642,6 +18541,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>74</v>
+      </c>
       <c r="Q245" t="b">
         <v>0</v>
       </c>
@@ -15704,6 +18616,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>45</v>
+      </c>
       <c r="Q246" t="b">
         <v>0</v>
       </c>
@@ -15766,6 +18691,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>56</v>
+      </c>
       <c r="Q247" t="b">
         <v>0</v>
       </c>
@@ -15828,6 +18766,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>50</v>
+      </c>
       <c r="Q248" t="b">
         <v>0</v>
       </c>
@@ -15890,6 +18841,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>51</v>
+      </c>
       <c r="Q249" t="b">
         <v>0</v>
       </c>
@@ -15952,6 +18916,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>55</v>
+      </c>
       <c r="Q250" t="b">
         <v>0</v>
       </c>
@@ -16014,6 +18991,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>48</v>
+      </c>
       <c r="Q251" t="b">
         <v>0</v>
       </c>
@@ -16076,6 +19066,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>37</v>
+      </c>
       <c r="Q252" t="b">
         <v>0</v>
       </c>
@@ -16139,7 +19142,7 @@
         </is>
       </c>
       <c r="Q253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
         <v>42</v>
@@ -16200,6 +19203,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>38</v>
+      </c>
       <c r="Q254" t="b">
         <v>0</v>
       </c>
@@ -16262,6 +19278,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>25</v>
+      </c>
       <c r="Q255" t="b">
         <v>0</v>
       </c>
@@ -16324,6 +19353,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>51</v>
+      </c>
       <c r="Q256" t="b">
         <v>0</v>
       </c>
@@ -16386,6 +19428,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>53</v>
+      </c>
       <c r="Q257" t="b">
         <v>0</v>
       </c>
@@ -16448,6 +19503,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>60</v>
+      </c>
       <c r="Q258" t="b">
         <v>0</v>
       </c>
@@ -16510,6 +19578,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>48</v>
+      </c>
       <c r="Q259" t="b">
         <v>0</v>
       </c>
@@ -16572,6 +19653,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>40</v>
+      </c>
       <c r="Q260" t="b">
         <v>0</v>
       </c>
@@ -16634,6 +19728,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>52</v>
+      </c>
       <c r="Q261" t="b">
         <v>0</v>
       </c>
@@ -16696,6 +19803,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>52</v>
+      </c>
       <c r="Q262" t="b">
         <v>0</v>
       </c>
@@ -16759,7 +19879,7 @@
         </is>
       </c>
       <c r="Q263" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R263" t="n">
         <v>42</v>
@@ -16820,6 +19940,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>62</v>
+      </c>
       <c r="Q264" t="b">
         <v>0</v>
       </c>
@@ -16882,6 +20015,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>26</v>
+      </c>
       <c r="Q265" t="b">
         <v>0</v>
       </c>
@@ -16944,6 +20090,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>27</v>
+      </c>
       <c r="Q266" t="b">
         <v>0</v>
       </c>
@@ -17006,6 +20165,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>37</v>
+      </c>
       <c r="Q267" t="b">
         <v>0</v>
       </c>
@@ -17068,6 +20240,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>37</v>
+      </c>
       <c r="Q268" t="b">
         <v>0</v>
       </c>
@@ -17130,6 +20315,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>42</v>
+      </c>
       <c r="Q269" t="b">
         <v>0</v>
       </c>
@@ -17192,6 +20390,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>54</v>
+      </c>
       <c r="Q270" t="b">
         <v>0</v>
       </c>
@@ -17254,6 +20465,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>50</v>
+      </c>
       <c r="Q271" t="b">
         <v>0</v>
       </c>
@@ -17316,6 +20540,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>56</v>
+      </c>
       <c r="Q272" t="b">
         <v>0</v>
       </c>
@@ -17378,6 +20615,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>44</v>
+      </c>
       <c r="Q273" t="b">
         <v>0</v>
       </c>
@@ -17441,7 +20691,7 @@
         </is>
       </c>
       <c r="Q274" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R274" t="n">
         <v>42</v>
@@ -17502,6 +20752,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>26</v>
+      </c>
       <c r="Q275" t="b">
         <v>0</v>
       </c>
@@ -17564,6 +20827,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>53</v>
+      </c>
       <c r="Q276" t="b">
         <v>0</v>
       </c>
@@ -17626,6 +20902,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>53</v>
+      </c>
       <c r="Q277" t="b">
         <v>0</v>
       </c>
@@ -17688,6 +20977,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>61</v>
+      </c>
       <c r="Q278" t="b">
         <v>0</v>
       </c>
@@ -17750,6 +21052,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>47</v>
+      </c>
       <c r="Q279" t="b">
         <v>0</v>
       </c>
@@ -17812,6 +21127,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>48</v>
+      </c>
       <c r="Q280" t="b">
         <v>0</v>
       </c>
@@ -17874,6 +21202,19 @@
           <t>PUDEP</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>45</v>
+      </c>
       <c r="Q281" t="b">
         <v>0</v>
       </c>
@@ -17936,6 +21277,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>31</v>
+      </c>
       <c r="Q282" t="b">
         <v>0</v>
       </c>
@@ -17998,6 +21352,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>31</v>
+      </c>
       <c r="Q283" t="b">
         <v>0</v>
       </c>
@@ -18060,6 +21427,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>78</v>
+      </c>
       <c r="Q284" t="b">
         <v>0</v>
       </c>
@@ -18122,6 +21502,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>37</v>
+      </c>
       <c r="Q285" t="b">
         <v>0</v>
       </c>
@@ -18184,6 +21577,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>25</v>
+      </c>
       <c r="Q286" t="b">
         <v>0</v>
       </c>
@@ -18247,7 +21653,7 @@
         </is>
       </c>
       <c r="Q287" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R287" t="n">
         <v>42</v>
@@ -18308,6 +21714,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>45</v>
+      </c>
       <c r="Q288" t="b">
         <v>0</v>
       </c>
@@ -18370,6 +21789,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>48</v>
+      </c>
       <c r="Q289" t="b">
         <v>0</v>
       </c>
@@ -18432,6 +21864,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>52</v>
+      </c>
       <c r="Q290" t="b">
         <v>0</v>
       </c>
@@ -18494,6 +21939,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>41</v>
+      </c>
       <c r="Q291" t="b">
         <v>0</v>
       </c>
@@ -18556,6 +22014,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>40</v>
+      </c>
       <c r="Q292" t="b">
         <v>0</v>
       </c>
@@ -18618,6 +22089,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>45</v>
+      </c>
       <c r="Q293" t="b">
         <v>0</v>
       </c>
@@ -18680,6 +22164,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>53</v>
+      </c>
       <c r="Q294" t="b">
         <v>0</v>
       </c>
@@ -18742,6 +22239,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>63</v>
+      </c>
       <c r="Q295" t="b">
         <v>1</v>
       </c>
@@ -18804,6 +22314,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>44</v>
+      </c>
       <c r="Q296" t="b">
         <v>0</v>
       </c>
@@ -18867,7 +22390,7 @@
         </is>
       </c>
       <c r="Q297" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R297" t="n">
         <v>42</v>
@@ -18928,6 +22451,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>26</v>
+      </c>
       <c r="Q298" t="b">
         <v>0</v>
       </c>
@@ -18990,6 +22526,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>56</v>
+      </c>
       <c r="Q299" t="b">
         <v>0</v>
       </c>
@@ -19052,6 +22601,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>36</v>
+      </c>
       <c r="Q300" t="b">
         <v>0</v>
       </c>
@@ -19114,6 +22676,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>42</v>
+      </c>
       <c r="Q301" t="b">
         <v>0</v>
       </c>
@@ -19176,6 +22751,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>52</v>
+      </c>
       <c r="Q302" t="b">
         <v>0</v>
       </c>
@@ -19238,6 +22826,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>49</v>
+      </c>
       <c r="Q303" t="b">
         <v>1</v>
       </c>
@@ -19300,6 +22901,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>74</v>
+      </c>
       <c r="Q304" t="b">
         <v>0</v>
       </c>
@@ -19362,6 +22976,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>34</v>
+      </c>
       <c r="Q305" t="b">
         <v>0</v>
       </c>
@@ -19424,6 +23051,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>31</v>
+      </c>
       <c r="Q306" t="b">
         <v>0</v>
       </c>
@@ -19486,6 +23126,19 @@
           <t>MNM</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>39</v>
+      </c>
       <c r="Q307" t="b">
         <v>0</v>
       </c>
@@ -19549,7 +23202,7 @@
         </is>
       </c>
       <c r="Q308" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R308" t="n">
         <v>42</v>
@@ -19610,6 +23263,19 @@
           <t>SDPI</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>33</v>
+      </c>
       <c r="Q309" t="b">
         <v>0</v>
       </c>
@@ -19672,6 +23338,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>45</v>
+      </c>
       <c r="Q310" t="b">
         <v>0</v>
       </c>
@@ -19734,6 +23413,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>39</v>
+      </c>
       <c r="Q311" t="b">
         <v>0</v>
       </c>
@@ -19796,6 +23488,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>48</v>
+      </c>
       <c r="Q312" t="b">
         <v>0</v>
       </c>
@@ -19858,6 +23563,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>63</v>
+      </c>
       <c r="Q313" t="b">
         <v>0</v>
       </c>
@@ -19920,6 +23638,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>59</v>
+      </c>
       <c r="Q314" t="b">
         <v>0</v>
       </c>
@@ -19982,6 +23713,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>66</v>
+      </c>
       <c r="Q315" t="b">
         <v>0</v>
       </c>
@@ -20044,6 +23788,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>42</v>
+      </c>
       <c r="Q316" t="b">
         <v>0</v>
       </c>
@@ -20106,6 +23863,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>26</v>
+      </c>
       <c r="Q317" t="b">
         <v>0</v>
       </c>
@@ -20169,7 +23939,7 @@
         </is>
       </c>
       <c r="Q318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R318" t="n">
         <v>42</v>
@@ -20230,6 +24000,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>47</v>
+      </c>
       <c r="Q319" t="b">
         <v>0</v>
       </c>
@@ -20292,6 +24075,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>63</v>
+      </c>
       <c r="Q320" t="b">
         <v>0</v>
       </c>
@@ -20354,6 +24150,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>30</v>
+      </c>
       <c r="Q321" t="b">
         <v>0</v>
       </c>
@@ -20416,6 +24225,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>43</v>
+      </c>
       <c r="Q322" t="b">
         <v>0</v>
       </c>
@@ -20478,6 +24300,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>42</v>
+      </c>
       <c r="Q323" t="b">
         <v>0</v>
       </c>
@@ -20540,6 +24375,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>45</v>
+      </c>
       <c r="Q324" t="b">
         <v>0</v>
       </c>
@@ -20602,6 +24450,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>49</v>
+      </c>
       <c r="Q325" t="b">
         <v>0</v>
       </c>
@@ -20664,6 +24525,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>43</v>
+      </c>
       <c r="Q326" t="b">
         <v>0</v>
       </c>
@@ -20727,7 +24601,7 @@
         </is>
       </c>
       <c r="Q327" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R327" t="n">
         <v>42</v>
@@ -20788,6 +24662,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>37</v>
+      </c>
       <c r="Q328" t="b">
         <v>0</v>
       </c>
@@ -20850,6 +24737,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>51</v>
+      </c>
       <c r="Q329" t="b">
         <v>0</v>
       </c>
@@ -20912,6 +24812,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>39</v>
+      </c>
       <c r="Q330" t="b">
         <v>0</v>
       </c>
@@ -20974,6 +24887,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>37</v>
+      </c>
       <c r="Q331" t="b">
         <v>0</v>
       </c>
@@ -21036,6 +24962,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>40</v>
+      </c>
       <c r="Q332" t="b">
         <v>0</v>
       </c>
@@ -21098,6 +25037,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>60</v>
+      </c>
       <c r="Q333" t="b">
         <v>0</v>
       </c>
@@ -21160,6 +25112,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>69</v>
+      </c>
       <c r="Q334" t="b">
         <v>0</v>
       </c>
@@ -21222,6 +25187,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>58</v>
+      </c>
       <c r="Q335" t="b">
         <v>0</v>
       </c>
@@ -21284,8 +25262,21 @@
           <t>SDPI</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>72</v>
+      </c>
       <c r="Q336" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R336" t="n">
         <v>42</v>
@@ -21347,7 +25338,7 @@
         </is>
       </c>
       <c r="Q337" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R337" t="n">
         <v>42</v>
@@ -21408,6 +25399,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>71</v>
+      </c>
       <c r="Q338" t="b">
         <v>0</v>
       </c>
@@ -21470,6 +25474,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>26</v>
+      </c>
       <c r="Q339" t="b">
         <v>0</v>
       </c>
@@ -21532,6 +25549,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>28</v>
+      </c>
       <c r="Q340" t="b">
         <v>0</v>
       </c>
@@ -21594,6 +25624,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>70</v>
+      </c>
       <c r="Q341" t="b">
         <v>0</v>
       </c>
@@ -21656,6 +25699,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>36</v>
+      </c>
       <c r="Q342" t="b">
         <v>0</v>
       </c>
@@ -21718,6 +25774,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>55</v>
+      </c>
       <c r="Q343" t="b">
         <v>0</v>
       </c>
@@ -21780,6 +25849,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>67</v>
+      </c>
       <c r="Q344" t="b">
         <v>0</v>
       </c>
@@ -21843,7 +25925,7 @@
         </is>
       </c>
       <c r="Q345" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R345" t="n">
         <v>42</v>
@@ -21904,6 +25986,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>63</v>
+      </c>
       <c r="Q346" t="b">
         <v>0</v>
       </c>
@@ -21966,6 +26061,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>39</v>
+      </c>
       <c r="Q347" t="b">
         <v>0</v>
       </c>
@@ -22028,6 +26136,19 @@
           <t>AMMKMNKZ</t>
         </is>
       </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>37</v>
+      </c>
       <c r="Q348" t="b">
         <v>0</v>
       </c>
@@ -22090,6 +26211,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>40</v>
+      </c>
       <c r="Q349" t="b">
         <v>0</v>
       </c>
@@ -22152,6 +26286,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>53</v>
+      </c>
       <c r="Q350" t="b">
         <v>0</v>
       </c>
@@ -22214,6 +26361,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>62</v>
+      </c>
       <c r="Q351" t="b">
         <v>0</v>
       </c>
@@ -22276,8 +26436,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>66</v>
+      </c>
       <c r="Q352" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R352" t="n">
         <v>42</v>
@@ -22338,6 +26511,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>41</v>
+      </c>
       <c r="Q353" t="b">
         <v>0</v>
       </c>
@@ -22400,6 +26586,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>63</v>
+      </c>
       <c r="Q354" t="b">
         <v>0</v>
       </c>
@@ -22461,6 +26660,19 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>52</v>
       </c>
       <c r="Q355" t="b">
         <v>0</v>

--- a/static/data/exports/Retro_PY_AE_2021.xlsx
+++ b/static/data/exports/Retro_PY_AE_2021.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P177" t="n">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P188" t="n">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P196" t="n">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16337,7 +16337,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16699,7 +16699,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17299,7 +17299,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -18036,7 +18036,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18773,7 +18773,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -18923,7 +18923,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -18998,7 +18998,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -19073,7 +19073,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P258" t="n">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20172,7 +20172,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20472,7 +20472,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -20909,7 +20909,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -21134,7 +21134,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21209,7 +21209,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21721,7 +21721,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22246,7 +22246,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22833,7 +22833,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -22983,7 +22983,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -23270,7 +23270,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23345,7 +23345,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P311" t="n">
@@ -23495,7 +23495,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23570,7 +23570,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23720,7 +23720,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24232,7 +24232,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -24382,7 +24382,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24532,7 +24532,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24669,7 +24669,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -24744,7 +24744,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -24819,7 +24819,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P330" t="n">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P332" t="n">
@@ -25044,7 +25044,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -25119,7 +25119,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -25194,7 +25194,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25406,7 +25406,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P340" t="n">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P341" t="n">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -25781,7 +25781,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -26068,7 +26068,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P347" t="n">
@@ -26143,7 +26143,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P348" t="n">
@@ -26218,7 +26218,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26293,7 +26293,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P350" t="n">
@@ -26368,7 +26368,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P351" t="n">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26518,7 +26518,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26593,7 +26593,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -26668,7 +26668,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P355" t="n">
